--- a/artfynd/A 54979-2021 artfynd.xlsx
+++ b/artfynd/A 54979-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54979-2021 artfynd.xlsx
+++ b/artfynd/A 54979-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110080285</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455413.1152714327</v>
+        <v>455413</v>
       </c>
       <c r="R2" t="n">
-        <v>6949376.709385827</v>
+        <v>6949377</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110080272</v>
+        <v>110080066</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455415.8943693995</v>
+        <v>455529</v>
       </c>
       <c r="R3" t="n">
-        <v>6949378.050412278</v>
+        <v>6949453</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +874,11 @@
         <v>110080195</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455449.6228891729</v>
+        <v>455450</v>
       </c>
       <c r="R4" t="n">
-        <v>6949388.164100999</v>
+        <v>6949389</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110080274</v>
+        <v>110080065</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455415.8943693995</v>
+        <v>455529</v>
       </c>
       <c r="R5" t="n">
-        <v>6949378.050412278</v>
+        <v>6949453</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1070,7 @@
         <v>110080214</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455435.100042444</v>
+        <v>455435</v>
       </c>
       <c r="R6" t="n">
-        <v>6949369.060466571</v>
+        <v>6949370</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,6 +1162,202 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110080272</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ladumyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>455416</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6949378</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110080274</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ladumyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>455416</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6949378</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54979-2021 artfynd.xlsx
+++ b/artfynd/A 54979-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080285</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080274</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,8 +1393,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110080065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>